--- a/outputs/evaluation/decision/v1/CF_M05/CF_M05_decision_eval_avg.xlsx
+++ b/outputs/evaluation/decision/v1/CF_M05/CF_M05_decision_eval_avg.xlsx
@@ -446,13 +446,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4861</v>
+        <v>0.7963</v>
       </c>
       <c r="C2" t="n">
-        <v>0.303</v>
+        <v>0.5128</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8483000000000001</v>
+        <v>0.8786</v>
       </c>
     </row>
     <row r="5">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.0944</v>
+        <v>0.3622</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.5667</v>
+        <v>0.6167</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9867</v>
+        <v>0.9496</v>
       </c>
     </row>
     <row r="8">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.7556</v>
+        <v>0.5262</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.6667</v>
+        <v>8.333299999999999</v>
       </c>
     </row>
     <row r="4">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.3333</v>
+        <v>6.6667</v>
       </c>
     </row>
     <row r="5">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.3333</v>
+        <v>1.6667</v>
       </c>
     </row>
     <row r="6">
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.6667</v>
+        <v>6.3333</v>
       </c>
     </row>
     <row r="7">
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4861</v>
+        <v>0.7963</v>
       </c>
     </row>
     <row r="8">
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.303</v>
+        <v>0.5128</v>
       </c>
     </row>
     <row r="9">

--- a/outputs/evaluation/decision/v1/CF_M05/CF_M05_decision_eval_avg.xlsx
+++ b/outputs/evaluation/decision/v1/CF_M05/CF_M05_decision_eval_avg.xlsx
@@ -446,13 +446,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7963</v>
+        <v>0.1179</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5128</v>
+        <v>0.0769</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8786</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.3622</v>
+        <v>0.125</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.6167</v>
+        <v>0.5834</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9496</v>
+        <v>0.9701</v>
       </c>
     </row>
     <row r="8">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.5262</v>
+        <v>0.75</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.333299999999999</v>
+        <v>7.3333</v>
       </c>
     </row>
     <row r="4">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.6667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.6667</v>
+        <v>6.3333</v>
       </c>
     </row>
     <row r="6">
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.3333</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7963</v>
+        <v>0.1179</v>
       </c>
     </row>
     <row r="8">
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5128</v>
+        <v>0.0769</v>
       </c>
     </row>
     <row r="9">
